--- a/AAII_Financials/Quarterly/MPC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MPC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>MPC</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>52083000</v>
+      </c>
+      <c r="E8" s="3">
         <v>34392000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>32796000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34875000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>33883000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>31620000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33203000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35156000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>37990000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32987000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>36537000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>41258000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>36612000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34941000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>40104000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>46186000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>54199000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>38402000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>35590000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>32613000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29827000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>22879000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18128000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17547000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>12298000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>22309000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>28082000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>27686000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>55819000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>28387000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>32524000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>23131000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>22442000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>18982000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>21238000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>19386000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>18347000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>16388000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>17278000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>16459000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>43064000</v>
+      </c>
+      <c r="E9" s="3">
         <v>31261000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>28861000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>31200000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30025000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>29360000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30558000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>32144000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>33945000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>29593000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>32582000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>34928000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31762000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>29294000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>33575000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>38821000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>44207000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>35068000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>32184000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>29563000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27177000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>21084000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>17216000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16673000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>11502000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>43294000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>51965000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>51595000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>79978000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>26084000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>28387000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>20537000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>19599000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>17484000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>21017000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>16766000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>16244000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>15044000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>15636000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>14967000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9019000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3131000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3935000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3675000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3858000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2260000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2645000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3012000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4045000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3394000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3955000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6330000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4850000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5647000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6529000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7365000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9992000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3334000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3406000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3050000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2650000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1795000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>912000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>874000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>796000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-20985000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-23883000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-23909000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-24159000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2303000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4137000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2594000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2843000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1498000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>221000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2620000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2103000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1344000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1642000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1492000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,55 +1496,58 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-422000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-6000</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-12000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-18000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-30000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-59000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-133000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-151000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-44000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2000</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1535,36 +1555,36 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>133000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>13000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>43000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-1024000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>251000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>12322000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1197000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1572,159 +1592,165 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>243000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>4000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>4000</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>86000</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
         <v>0</v>
       </c>
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>838000</v>
+      </c>
+      <c r="E15" s="3">
         <v>809000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>828000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>841000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>789000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>793000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>826000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>846000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>838000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>827000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>828000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>845000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>834000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>800000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>797000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>794000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>819000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>805000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>813000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>823000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>828000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>844000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>849000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>830000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>833000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>863000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>850000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>761000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1614000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>919000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>874000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>555000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>533000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>528000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>540000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>517000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>521000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>536000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>504000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>45020000</v>
+      </c>
+      <c r="E17" s="3">
         <v>33169000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>30734000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>33142000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31910000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31168000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32317000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34016000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35829000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31416000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34407000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36810000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>33494000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>30993000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35367000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>39500000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>45871000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>36686000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>33945000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>31273000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28862000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22662000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>17729000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18604000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>11723000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>34464000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>27524000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>26006000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>53595000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>27718000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>30567000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21728000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>20731000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>18546000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>20070000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>17810000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>17365000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>16096000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>16725000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>16024000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7063000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1223000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2062000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1733000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1973000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>452000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>886000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1140000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2161000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1571000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2130000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4448000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3118000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3948000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4737000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6686000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8328000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1716000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1645000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1340000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>965000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>217000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>399000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1057000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>575000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-12155000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>558000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1680000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2224000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>669000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1957000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1403000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1711000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>436000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1168000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1576000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>982000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>292000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>553000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>435000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-254000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-164000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-203000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-972000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-205000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-219000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-244000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-205000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-360000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-203000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-190000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-215000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-198000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-127000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>122000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>63000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-13000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>25000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-15000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-54000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>8000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-28000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>16000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-45000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8155000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2196000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3093000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3546000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2967000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1464000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1956000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2191000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3359000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2601000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3148000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5508000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4150000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4875000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5656000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7543000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9134000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2546000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2463000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2161000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1782000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1042000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1240000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-443000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1506000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-11207000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1544000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2528000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4030000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1590000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2832000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1930000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2262000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>980000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1663000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2094000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1500000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>826000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1051000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>939000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>394000</v>
+      </c>
+      <c r="E22" s="3">
         <v>386000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>377000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>341000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>337000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>334000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>314000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>337000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>328000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>329000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>318000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>320000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>316000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>311000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>306000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>303000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>299000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>287000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>302000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>313000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>318000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>334000</v>
       </c>
       <c r="Y22" s="3">
         <v>334000</v>
       </c>
       <c r="Z22" s="3">
+        <v>334000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>344000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>337000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>318000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>305000</v>
       </c>
       <c r="AD22" s="3">
         <v>305000</v>
       </c>
       <c r="AE22" s="3">
+        <v>305000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>621000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>308000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>326000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>212000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>213000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>195000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>164000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>158000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>155000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>148000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>130000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6982000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1034000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2351000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2403000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1878000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>383000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>896000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1128000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2328000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1605000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2284000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4635000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3163000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3907000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4553000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6446000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8016000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1454000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1348000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1012000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>593000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-136000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>57000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>234000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-12487000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>261000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1368000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1604000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>363000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1632000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1163000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1516000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>257000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>959000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1419000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>824000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>142000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>417000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>294000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1444000</v>
+      </c>
+      <c r="E24" s="3">
         <v>183000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>372000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>460000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>268000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>37000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>111000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>113000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>373000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>293000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>407000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1004000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>583000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>823000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>984000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1426000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1799000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>282000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>243000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-18000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>34000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-193000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-436000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>150000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1951000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>184000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>255000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>345000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>104000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>437000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>222000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>281000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>22000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>334000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>415000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>250000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>41000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>128000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>75000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5538000</v>
+      </c>
+      <c r="E26" s="3">
         <v>851000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1979000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1943000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1610000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>346000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>785000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1015000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1955000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1312000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1877000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3631000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2580000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3084000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3569000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5020000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6217000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1172000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1105000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1030000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>588000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-170000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>250000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-980000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>84000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10536000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>77000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1113000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1259000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>259000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1195000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>941000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1235000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>235000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>625000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1004000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>574000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>101000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>289000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>219000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5133000</v>
+      </c>
+      <c r="E27" s="3">
         <v>511000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1534000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1368000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1215000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-74000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>370000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>622000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1514000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>936000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1449000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3278000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2225000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2720000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3247000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4475000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5870000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>845000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>772000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>694000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>298000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-476000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-40000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1257000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-183000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-9552000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>256000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>841000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>733000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>951000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>737000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1054000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>37000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>515000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>903000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>483000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>30000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>227000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>145000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3195,11 +3256,11 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>72000</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -3213,34 +3274,34 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>8214000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>234000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>324000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>371000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>702000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>318000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>185000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>254000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>367000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>1500000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>254000</v>
+      </c>
+      <c r="E32" s="3">
         <v>164000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>203000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>972000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>205000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>219000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>244000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>205000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>360000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>203000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>190000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>215000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>198000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>127000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-122000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-63000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>13000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-25000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>15000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>54000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>19000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>8000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>15000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>14000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>7000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>28000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>45000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>3000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>2000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>6000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5138000</v>
+      </c>
+      <c r="E33" s="3">
         <v>511000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1535000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1370000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1216000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-74000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>371000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>622000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1515000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>937000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1451000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3280000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2226000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2724000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3319000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4475000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5870000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>845000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>772000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>694000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8512000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-242000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>284000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-886000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>519000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-9234000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>441000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1095000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1100000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>951000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>737000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1054000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>37000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2015000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>903000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>483000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>30000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>227000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>145000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5138000</v>
+      </c>
+      <c r="E35" s="3">
         <v>511000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1535000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1370000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1216000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-74000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>371000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>622000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1515000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>937000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1451000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3280000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2226000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2724000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3319000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4475000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5870000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>845000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>772000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>694000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8512000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-242000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>284000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-886000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>519000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-9234000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>441000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1095000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1100000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>951000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>737000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1054000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>37000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2015000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>903000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>483000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>30000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>227000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>145000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7768000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2151000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3672000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2654000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1673000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3812000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3210000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4002000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4441000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3175000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5443000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8452000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7345000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7960000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8625000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7376000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9078000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7148000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5291000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5874000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11839000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>624000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>415000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>618000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1091000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1393000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1525000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1247000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>877000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1687000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4992000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4999000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4653000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3011000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2088000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1450000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2167000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>887000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>709000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4365,49 +4455,49 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>1141000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4058000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4399000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4781000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4604000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4109000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3492000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3145000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3759000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4241000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3449000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>5548000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7352000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>5418000</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>8</v>
@@ -4424,8 +4514,8 @@
       <c r="AC42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -4463,763 +4553,784 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15740000</v>
+      </c>
+      <c r="E43" s="3">
         <v>14629000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10317000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10487000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11128000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12114000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11145000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10180000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12307000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13171000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12187000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12469000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10274000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10143000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13477000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13458000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>17305000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>15661000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11034000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9511000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9771000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7468000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5760000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4911000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4361000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5583000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7233000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7461000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7603000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6893000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5853000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5408000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4919000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4613000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4695000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3900000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3259000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3284000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3617000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3136000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9973000</v>
+      </c>
+      <c r="E44" s="3">
         <v>10764000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10129000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9829000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10106000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10488000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9568000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9886000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9800000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9781000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9317000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10143000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9536000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10268000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8827000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>9834000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>11048000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>9482000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8055000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>9211000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8879000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8407000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7999000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7403000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>8086000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>7445000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>10031000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>9696000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>9088000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>9833000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>9837000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5339000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5485000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5111000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5550000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>5493000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>5548000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>5392000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>5656000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>5524000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>805000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1154000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>662000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1660000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>821000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>726000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>524000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>740000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>741000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>732000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>403000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>607000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>949000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>618000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1168000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>858000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>741000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>648000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>568000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2195000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2685000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>13862000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14113000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>13268000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1105000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>975000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12556000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>457000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>458000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>548000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>646000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>134000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>145000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>148000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>145000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>150000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>186000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>199000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>241000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34286000</v>
+      </c>
+      <c r="E46" s="3">
         <v>28698000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24780000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24630000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23728000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27140000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>24447000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25949000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>31347000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>31260000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32131000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36275000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>32213000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32486000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>35242000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>35285000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>42413000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>36388000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>30496000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>34143000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>38592000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>30361000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>28287000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>26200000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14643000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15693000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>30458000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>19139000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>18396000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>18151000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>18023000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>15873000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>15548000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>14525000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>13401000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>11631000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>10443000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>11042000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>10401000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>9545000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7197000</v>
+      </c>
+      <c r="E47" s="3">
         <v>6999000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6795000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6900000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7294000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7095000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6857000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6976000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6821000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6831000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6260000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6521000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6665000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6626000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6466000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6493000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5508000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5514000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>5409000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5384000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5424000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5435000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5422000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5462000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5740000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5656000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6568000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6725000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6729000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6558000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5898000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4910000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4838000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4817000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>4787000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>4769000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>4824000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>4704000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>3827000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>3554000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39428000</v>
+      </c>
+      <c r="E48" s="3">
         <v>39104000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38890000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38357000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36204000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36192000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36328000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35734000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35873000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36218000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36345000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>36000000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>36347000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36660000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36871000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>36584000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>38338000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>38476000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>38812000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>39054000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>39496000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>40005000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>40556000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>41397000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>47479000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>47895000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>107072000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>47556000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>47923000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>47771000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>45058000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>27717000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>26931000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>26618000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>26443000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>26036000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>25786000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>25669000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>25765000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>25697000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11928000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11993000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12068000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12080000</v>
-      </c>
-      <c r="G49" s="3">
-        <v>8244000</v>
       </c>
       <c r="H49" s="3">
         <v>8244000</v>
       </c>
       <c r="I49" s="3">
+        <v>8244000</v>
+      </c>
+      <c r="J49" s="3">
         <v>10018000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>8244000</v>
       </c>
       <c r="K49" s="3">
         <v>8244000</v>
@@ -5249,7 +5360,7 @@
         <v>8244000</v>
       </c>
       <c r="T49" s="3">
-        <v>8256000</v>
+        <v>8244000</v>
       </c>
       <c r="U49" s="3">
         <v>8256000</v>
@@ -5270,31 +5381,31 @@
         <v>8256000</v>
       </c>
       <c r="AA49" s="3">
-        <v>12710000</v>
+        <v>8256000</v>
       </c>
       <c r="AB49" s="3">
         <v>12710000</v>
       </c>
       <c r="AC49" s="3">
+        <v>12710000</v>
+      </c>
+      <c r="AD49" s="3">
         <v>15650000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>21277000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>20277000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>20229000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>20184000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3713000</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>3586000</v>
       </c>
       <c r="AJ49" s="3">
         <v>3586000</v>
@@ -5312,13 +5423,16 @@
         <v>3586000</v>
       </c>
       <c r="AO49" s="3">
+        <v>3586000</v>
+      </c>
+      <c r="AP49" s="3">
         <v>3587000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>3648000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1365000</v>
+        <v>1471000</v>
       </c>
       <c r="E52" s="3">
+        <v>1393000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1419000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1273000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3014000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2962000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1206000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2930000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2944000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2975000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3006000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2929000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2973000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3021000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3081000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3088000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2234000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2318000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2400000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2463000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2532000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2594000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2637000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2705000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4021000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4363000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3204000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3442000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3571000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3727000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3777000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>818000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>833000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>818000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>830000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>784000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>808000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>820000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>833000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>849000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>94310000</v>
+      </c>
+      <c r="E54" s="3">
         <v>88187000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>83955000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>83240000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78484000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>81633000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78858000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>79833000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>85229000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>85528000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>85987000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>89969000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>86442000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>87037000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>89904000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>89694000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>96737000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>90952000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>85373000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>89300000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>94300000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>86651000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>85158000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>84020000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>84593000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>86317000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>98556000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>98139000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>96896000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>96436000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>92940000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>53031000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>51736000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>50364000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>49047000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>46806000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>45447000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>45821000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>44413000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>43293000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,225 +6145,229 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19227000</v>
+      </c>
+      <c r="E57" s="3">
         <v>17617000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12974000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12486000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13345000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14748000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13906000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12763000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14865000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15471000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13761000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15839000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13052000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13031000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15312000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16682000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>22502000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19791000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13700000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12196000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12170000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9953000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7803000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6701000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6110000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8106000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11222000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11380000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10905000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10568000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9366000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8016000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8113000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>7066000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>8297000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>6159000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>5307000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>5343000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>5593000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>5055000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2619000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2620000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2860000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2053000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2265000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4475000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3466000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4652000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5366000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2929000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2408000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1272000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>495000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>479000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1066000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1064000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1087000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1075000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>571000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>73000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>70000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1786000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2854000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2500000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1715000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1710000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1415000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>557000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>554000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>550000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>544000</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>26000</v>
       </c>
       <c r="AI58" s="3">
         <v>26000</v>
@@ -6242,16 +6376,16 @@
         <v>26000</v>
       </c>
       <c r="AK58" s="3">
+        <v>26000</v>
+      </c>
+      <c r="AL58" s="3">
         <v>624000</v>
-      </c>
-      <c r="AL58" s="3">
-        <v>29000</v>
       </c>
       <c r="AM58" s="3">
         <v>29000</v>
       </c>
       <c r="AN58" s="3">
-        <v>28000</v>
+        <v>29000</v>
       </c>
       <c r="AO58" s="3">
         <v>28000</v>
@@ -6259,496 +6393,511 @@
       <c r="AP58" s="3">
         <v>28000</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>28000</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4291000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2646000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2288000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2892000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2520000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2058000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2045000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2396000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2677000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1949000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2866000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3645000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2047000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2911000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3642000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3568000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4848000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4254000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3627000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4629000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7272000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4346000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5006000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5045000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3679000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3753000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5919000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3402000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3431000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4029000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3306000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1592000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1576000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1280000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1557000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1459000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1422000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1495000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1525000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1257000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27421000</v>
+      </c>
+      <c r="E60" s="3">
         <v>24411000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19678000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18728000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19255000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22725000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20827000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21068000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24000000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21787000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20150000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21735000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17466000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17057000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>20020000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21314000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>28437000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>25120000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>17898000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>16898000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>19512000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>16085000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>15663000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14246000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11504000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13569000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16948000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15339000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14890000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15147000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13216000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9634000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9715000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>8372000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>10478000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7647000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>6758000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>6866000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>7146000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>6340000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>31673000</v>
+      </c>
+      <c r="E61" s="3">
         <v>31706000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>31498000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32150000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>27770000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27662000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25292000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24744000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24745000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25602000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26093000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27311000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28070000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28063000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>25634000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>25638000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>25687000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>25634000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24968000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>27270000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>28250000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>30694000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28730000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>29377000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>30451000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>29899000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28020000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28282000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>27853000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>27565000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>26980000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>18423000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>17241000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>17232000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>12322000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>12753000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>12577000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>12570000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>10544000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>10538000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2255000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1417000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1536000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1377000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1246000</v>
       </c>
       <c r="H62" s="3">
         <v>1246000</v>
       </c>
       <c r="I62" s="3">
+        <v>1246000</v>
+      </c>
+      <c r="J62" s="3">
         <v>1305000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1352000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1358000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1355000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1409000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1341000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1244000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1214000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9163000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8967000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8944000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8899000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8926000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9168000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9845000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>10393000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>10545000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9883000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>10821000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>10653000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11746000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>10894000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>10087000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9862000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7691000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4940000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4959000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4897000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4419000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5604000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>5548000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>5588000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>5520000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>5458000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>68590000</v>
+      </c>
+      <c r="E66" s="3">
         <v>64760000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>59869000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>59351000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55220000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>58568000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54352000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>54121000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>57141000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>55757000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>54588000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>57171000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53874000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>53374000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>62189000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>63390000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>70431000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>66980000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>59167000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>61020000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>65379000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>65059000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>62959000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>61567000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>60852000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>62229000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>64862000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>64401000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>62689000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>62485000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>57765000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>37865000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>36778000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>35376000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>35014000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>33876000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>32811000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>32751000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>30856000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>29898000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>44812000</v>
+      </c>
+      <c r="E72" s="3">
         <v>39966000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>39751000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>38517000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>37424000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>36489000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>36848000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>36771000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>36423000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>35199000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>34562000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>33424000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>30442000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>28528000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>26142000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>23175000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18983000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13420000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12905000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12484000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12160000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4029000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4650000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4744000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6008000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6380000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15990000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15891000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15146000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>14391000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14755000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>14119000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13589000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12745000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>12864000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>11044000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>10344000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>10046000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>10206000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>10169000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19077000</v>
+      </c>
+      <c r="E76" s="3">
         <v>16753000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17314000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17097000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16624000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16396000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17745000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18933000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21324000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22922000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24404000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25862000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25714000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26858000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>27715000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26304000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26306000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23972000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>26206000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>28280000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>28921000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21592000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>22199000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>22453000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>23741000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24088000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>33694000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>33738000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>34207000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>33951000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>35175000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15166000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14958000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14988000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14033000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12930000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>12636000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>13070000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>13557000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>13395000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5138000</v>
+      </c>
+      <c r="E81" s="3">
         <v>511000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1535000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1370000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1216000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-74000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>371000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>622000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1515000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>937000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1451000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3280000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2226000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2724000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3319000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4475000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5870000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>845000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>772000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>694000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8512000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-242000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>284000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-886000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>519000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-9234000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>441000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1095000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1100000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>951000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>737000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1054000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>37000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2015000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>903000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>483000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>30000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>227000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>145000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>789000</v>
+      </c>
+      <c r="E83" s="3">
         <v>793000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>560000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>846000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>838000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>827000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>512000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>845000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>834000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>800000</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>794000</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>805000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>797000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>794000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>819000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>805000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>813000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>836000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>871000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>844000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>849000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>629000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>935000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>962000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>978000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>855000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1805000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>919000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>874000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>555000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>533000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>528000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>540000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>517000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>521000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>536000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>504000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10327000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1121000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3069000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2609000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2639000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-64000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2207000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1684000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3242000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1532000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1123000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4953000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3984000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4057000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4382000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2514000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6952000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2513000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3674000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1148000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1380000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>454000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1328000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1321000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>538000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-768000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2409000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2787000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4245000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1623000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2727000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1182000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2386000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-137000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2745000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1905000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>849000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1113000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>993000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>412000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1186000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-913000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1181000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-947000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-695000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-663000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-810000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-651000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-487000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-585000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-532000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-420000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-481000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-457000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-726000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-701000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-498000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-495000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-481000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-377000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-302000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-304000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-457000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-420000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-848000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1551000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1404000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2419000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1241000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1263000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-849000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-711000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-755000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-804000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-663000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-655000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1220000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1490000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-2863000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1394000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-214000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3756000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-974000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-923000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>307000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2034000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>17000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-824000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-964000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-435000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-880000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-816000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-498000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>501000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1088000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1708000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1448000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2054000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>15670000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-267000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-433000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-747000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-989000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1088000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1686000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1695000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2880000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1520000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4775000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1377000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-740000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-778000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-779000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-603000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-659000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1353000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-724000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-721000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,121 +10455,122 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E96" s="3">
         <v>295000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>300000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>276000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>279000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>285000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>292000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>273000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>290000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>299000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>311000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>297000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>316000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>337000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-351000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-285000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-313000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-330000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-354000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-370000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-381000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-379000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-377000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-378000</v>
       </c>
       <c r="AA96" s="3">
         <v>-378000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-378000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-377000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-344000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-348000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-706000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-354000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-317000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-211000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-219000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-202000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-186000</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-190000</v>
       </c>
       <c r="AO96" s="3">
         <v>-190000</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>-190000</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-190000</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3316000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1596000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1836000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2127000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3804000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1589000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3307000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4157000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1993000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2977000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3169000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3411000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3720000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3907000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2636000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4715000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3932000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2364000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5703000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2762000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5970000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>16000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-949000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-150000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2021000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-722000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-813000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1841000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-920000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1222000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>186000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1299000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2557000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-660000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-910000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1523000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-89000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-729000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5617000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1522000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1019000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>980000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2139000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>602000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-793000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-439000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1266000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2269000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3010000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1107000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-616000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-666000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1248000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1700000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1932000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1857000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-581000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5964000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>11080000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>203000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-162000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-375000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-601000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>165000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>279000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-476000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-817000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3270000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>347000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1642000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>921000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>640000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-717000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1280000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>178000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1045000</v>
       </c>
     </row>
